--- a/core/public/static/test-files/超多列.xlsx
+++ b/core/public/static/test-files/超多列.xlsx
@@ -1,22 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="测试用例" sheetId="1" r:id="rId1"/>
     <sheet name="测试需求" sheetId="2" r:id="rId2"/>
     <sheet name="功能模块" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16718" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16654" uniqueCount="132">
   <si>
     <t>用例ID
 （选填，不填将新建，否则会更新旧用例）</t>
@@ -83,10 +96,7 @@
 （选填，100字符）</t>
   </si>
   <si>
-    <t>【产品集成评测管理v1.7.1】【测试结果】【新建】基本信息简化，只反显成果编码和提测版本号</t>
-  </si>
-  <si>
-    <t>功能性</t>
+    <t>性能效率</t>
   </si>
   <si>
     <t>P1</t>
@@ -101,26 +111,10 @@
     <t>成果A可创建测试结果</t>
   </si>
   <si>
-    <t>1.登录系统
-2.【测试结果】新建，成果选择成果A，查看基本信息反显
-3.查看系基本信息其他反显字段</t>
-  </si>
-  <si>
-    <t>1.登录系统成功
-2.进入新建页面正常，选择成果A后，反显产品编码（ABC123）,提测版本号(v1.0.0)
-3.原二开等级、首次提测时间、准入审查次数、下发测试类型、计划名称、参与执行人、提测要求时间、提测人、最终提测时间、测试基地、测试负责人、测试完成时间字段不展示，也不反显</t>
-  </si>
-  <si>
     <t>系统测试</t>
   </si>
   <si>
     <t>关键测试项</t>
-  </si>
-  <si>
-    <t>【产品集成评测管理v1.7.1】【测试结果】【详情】基本信息简化，只反显成果编码和提测版本号</t>
-  </si>
-  <si>
-    <t>性能效率</t>
   </si>
   <si>
     <t>新建需求-测试结果2</t>
@@ -129,31 +123,10 @@
     <t>成果A已创建测试结果</t>
   </si>
   <si>
-    <t>1.登录系统
-2.【测试结果】列表，点击成果A&lt;详情&gt;按钮进入成果A测试结果详情页面，查看基本信息反显
-3.查看系基本信息其他反显字段</t>
-  </si>
-  <si>
-    <t>1.登录系统成功
-2.进入详情页面正常，基本信息位置只显示&lt;产品类型&gt;、&lt;产品名称&gt;、&lt;测试轮次&gt;、产品编码（ABC123）,提测版本号(v1.0.0)
-3.原二开等级、首次提测时间、准入审查次数、下发测试类型、计划名称、参与执行人、提测要求时间、提测人、最终提测时间、测试基地、测试负责人、测试完成时间字段不展示，也不反显</t>
-  </si>
-  <si>
-    <t>【产品集成评测管理v1.7.1】【测试结果】【编辑】基本信息简化，只反显成果编码和提测版本号</t>
-  </si>
-  <si>
     <t>兼容性</t>
   </si>
   <si>
     <t>新建需求-测试结果3</t>
-  </si>
-  <si>
-    <t>1.登录系统
-2.【测试结果】列表，点击成果A&lt;编辑&gt;按钮进入成果A测试结果编辑页面，查看基本信息反显
-3.查看系基本信息其他反显字段</t>
-  </si>
-  <si>
-    <t>【产品集成评测管理v1.7.1】【测试结果】历史数据编辑、详情、新建、基本信息简化，只反显成果编码和提测版本号</t>
   </si>
   <si>
     <t>易用性</t>
@@ -165,53 +138,16 @@
     <t>存在历史数据成果B</t>
   </si>
   <si>
-    <t>1.登录系统
-2.【测试结果】列表，点击成果B&lt;新建&gt;按钮进入成果A测试结果详情页面，查看基本信息反显
-3.【测试结果】列表，点击成果B&lt;详情&gt;按钮进入成果A测试结果详情页面，查看基本信息反显
-4.【测试结果】列表，点击成果B&lt;编辑&gt;按钮进入成果A测试结果详情页面，查看基本信息反显
-5.查看系基本信息其他反显字段</t>
-  </si>
-  <si>
-    <t>1.登录系统成功
-2.进入新建页面正常，基本信息位置只显示&lt;产品类型&gt;、&lt;产品名称&gt;、&lt;测试轮次&gt;、产品编码（ABC123）,提测版本号(v1.0.0)
-3.进入详情页面正常，基本信息位置只显示&lt;产品类型&gt;、&lt;产品名称&gt;、&lt;测试轮次&gt;、产品编码（ABC123）,提测版本号(v1.0.0)
-4.进入编辑页面正常，基本信息位置只显示&lt;产品类型&gt;、&lt;产品名称&gt;、&lt;测试轮次&gt;、产品编码（ABC123）,提测版本号(v1.0.0)
-5.原二开等级、首次提测时间、准入审查次数、下发测试类型、计划名称、参与执行人、提测要求时间、提测人、最终提测时间、测试基地、测试负责人、测试完成时间字段不展示，也不反显</t>
-  </si>
-  <si>
-    <t>【产品集成评测管理v1.7.1】【测试结果】历史数据编辑、详情、新建、基1232123</t>
-  </si>
-  <si>
     <t>可靠性</t>
   </si>
   <si>
     <t>新建需求-测试结果5</t>
   </si>
   <si>
-    <t>【产品集成评测管理v1.7.1】【测试结果】测试报告中基本信息中所有字段不变</t>
-  </si>
-  <si>
     <t>信息安全性</t>
   </si>
   <si>
     <t>新建需求-测试结果6</t>
-  </si>
-  <si>
-    <t>1.登录系统
-2.【测试结果】列表，点击成果B&lt;详情&gt;按钮进入成果A测试结果详情页面
-3.点击查看报告进入测试报告界面
-4.点击下载报告
-5.查看测试报告中的基本信息模块数据</t>
-  </si>
-  <si>
-    <t>1.登录系统成功
-2.进入详情页面正常，基本信息位置只显示&lt;产品类型&gt;、&lt;产品名称&gt;、&lt;测试轮次&gt;、产品编码（ABC123）,提测版本号(v1.0.0)
-3.展示测试报告正常，基本信息模块正常展示产品类型、产品名称、测试轮次、二开等级、首次提测时间、准入审查次数、下发测试类型、计划名称、参与执行人、产品编码、提测要求时间、提测版本号、提测人、最终提测时间、测试基地、测试负责人、测试完成时间，且数据正确
-4.下载测试报告正常
-5.下载成功的本地测试报告打开正常，基本信息模块正常展示产品类型、产品名称、测试轮次、二开等级、首次提测时间、准入审查次数、下发测试类型、计划名称、参与执行人、产品编码、提测要求时间、提测版本号、提测人、最终提测时间、测试基地、测试负责人、测试完成时间，且数据正确</t>
-  </si>
-  <si>
-    <t>【产品集成评测管理v1.7.1】【测试结果】【新建】-正常轮次创建测试结果，测试结论枚举值为通过/不通过</t>
   </si>
   <si>
     <t>维护性</t>
@@ -223,19 +159,6 @@
     <t>成果A一轮测试创建测试结果</t>
   </si>
   <si>
-    <t>1.登录系统
-2.【测试结果】-新建，选择成果A
-3.点击&lt;测试结论&gt;输入框，查看枚举值</t>
-  </si>
-  <si>
-    <t>1.登录系统成功
-2.进入【测试结果】新建页面成功，选择成果A后，正常显示成果A的版本号和成果编码
-3.&lt;测试结论&gt;枚举值显示通过/不通过,能够正常单选，点击保存创建测试结果成功，数据展示在测试结果列表中</t>
-  </si>
-  <si>
-    <t>【产品集成评测管理v1.7.1】【测试结果】【新建】-成果复测创建测试结果，测试结论枚举值为复测通过/复测不通过</t>
-  </si>
-  <si>
     <t>可移植性</t>
   </si>
   <si>
@@ -243,19 +166,6 @@
   </si>
   <si>
     <t>成果B复测创建测试结果</t>
-  </si>
-  <si>
-    <t>1.登录系统
-2.【测试结果】-新建，选择成果B
-3.点击&lt;测试结论&gt;输入框，查看枚举值</t>
-  </si>
-  <si>
-    <t>1.登录系统成功
-2.进入【测试结果】新建页面成功，选择成果B后，正常显示成果B的版本号和成果编码
-3.&lt;测试结论&gt;枚举值显示复测通过/复测不通过,能够正常单选，点击保存创建测试结果成功，数据展示在测试结果列表中</t>
-  </si>
-  <si>
-    <t>【产品集成评测管理v1.7.1】【测试结果】【新建】-测试类型多选时，测试项通过表展示多个表正确</t>
   </si>
   <si>
     <t>业务场景</t>
@@ -267,31 +177,10 @@
     <t>推送成果A，下发测试类型为国标、企标、及其他自定义类型</t>
   </si>
   <si>
-    <t>1.登录系统
-2.【测试结果】-新建，选择成果A
-3.查看测试结论位置测试项通过表展示</t>
-  </si>
-  <si>
-    <t>1.登录系统成功
-2.进入新建界面成功，选择成果A后正常展示成果A的版本号和成果编码
-3.&lt;测试结论&gt;位置测试项通过表展示正常，个数与下发的测试类型选择的个数一致</t>
-  </si>
-  <si>
-    <t>【产品集成评测管理v1.7.1】【测试结果】【新建】-调度下发测试类型多选时（大于等于4），测试项通过表展示多个表正确</t>
-  </si>
-  <si>
     <t>接口(OpenAPI)</t>
   </si>
   <si>
     <t>新建需求-测试结果10</t>
-  </si>
-  <si>
-    <t>1.登录系统成功
-2.进入新建界面成功，选择成果A后正常展示成果A的版本号和成果编码
-3.&lt;测试结论&gt;位置测试项通过表展示正常，个数与下发的测试类型选择的个数一致，各个表宽度一致</t>
-  </si>
-  <si>
-    <t>【产品集成评测管理v1.7.1】【测试结果】【新建】-调度下发测试类型单独选指标单选，测试项通过表展示正确</t>
   </si>
   <si>
     <t>二开能力</t>
@@ -303,14 +192,6 @@
     <t>推送成果A，下发测试类型为国标，指标选择功能性</t>
   </si>
   <si>
-    <t>1.登录系统成功
-2.进入新建界面成功，选择成果A后正常展示成果A的版本号和成果编码
-3.&lt;测试结论&gt;位置测试项通过表展示正常，通过表个数为1，名称测试类型：国家标准，测试项为功能性，列表定宽定高</t>
-  </si>
-  <si>
-    <t>【产品集成评测管理v1.7.1】【测试结果】【新建】-调度下发测试类型选择国标，测试项勾选超过10项测试项通过表展示正确</t>
-  </si>
-  <si>
     <t>研发全流程上云</t>
   </si>
   <si>
@@ -320,32 +201,16 @@
     <t>成果A下发测试类型选择国标，勾选10个以上指标</t>
   </si>
   <si>
-    <t>1.登录系统成功
-2.进入新建界面成功，选择成果A后正常展示成果A的版本号和成果编码
-3.&lt;测试结论&gt;位置测试项通过表展示正常，通过表个数为1，名称测试类型：国家标准，测试项展示勾选的10个以上测试项，表格自动增高展示所有</t>
-  </si>
-  <si>
     <t>研发云CI/CD</t>
   </si>
   <si>
     <t>新建需求-测试结果13</t>
   </si>
   <si>
-    <t>【产品集成评测管理v1.7.1】【测试结果】【新建】-调度下发选择的测试类型文字较长，勾选的指标名称文字较长，验证测试项通过表展示</t>
-  </si>
-  <si>
     <t>组件适配能力</t>
   </si>
   <si>
     <t>新建需求-测试结果14</t>
-  </si>
-  <si>
-    <t>1.登录系统成功
-2.进入新建界面成功，选择成果A后正常展示成果A的版本号和成果编码
-3.&lt;测试结论&gt;表宽根据测试类型名称长度和测试项名称长度自动加宽</t>
-  </si>
-  <si>
-    <t>【产品集成评测管理v1.7.1】【测试结果】【新建】-测试项全部选择不通过，测试结论选择通过</t>
   </si>
   <si>
     <t>底座集成能力</t>
@@ -357,52 +222,10 @@
     <t>成果A下发测试类型选择国标8项</t>
   </si>
   <si>
-    <t>1.登录系统
-2.【测试结果】-新建，选择成果A
-3.测试结论选择通过
-4.所有测试项勾选不通过
-5.提交测试结果
-6.更改结论为不通过
-7.提交测试结果</t>
-  </si>
-  <si>
-    <t>1.登录系统成功
-2.进入新建界面成功，选择成果A后正常展示成果A的版本号和成果编码
-3.&lt;测试结论&gt;选择通过成功
-4.所有测试项勾选不通过成功
-5.提交报错或者提示用户测试结论与实际不符
-6.更改结论为不通过成功
-7.提交测试结果成功</t>
-  </si>
-  <si>
-    <t>【产品集成评测管理v1.7.1】【测试结果】【新建】-测试项部分选择不通过，测试结论选择通过</t>
-  </si>
-  <si>
     <t>用户文档集</t>
   </si>
   <si>
     <t>新建需求-测试结果16</t>
-  </si>
-  <si>
-    <t>1.登录系统
-2.【测试结果】-新建，选择成果A
-3.测试结论选择通过
-4.测试项功能性、性能效率勾选不通过
-5.提交测试结果
-6.更改测试结论为不通过
-7.提交测试结果</t>
-  </si>
-  <si>
-    <t>1.登录系统成功
-2.进入新建界面成功，选择成果A后正常展示成果A的版本号和成果编码
-3.&lt;测试结论&gt;选择通过成功
-4.测试项功能性、性能效率勾选不通过成功
-5.提交报错或者提示用户测试结论与实际不符
-6.更改测试结论为不通过成功
-7.提交测试结果成功</t>
-  </si>
-  <si>
-    <t>【产品集成评测管理v1.7.1】【测试结果】【新建】-测试项全部选择通过，测试结论选择不通过</t>
   </si>
   <si>
     <t>病毒扫描</t>
@@ -411,43 +234,16 @@
     <t>新建需求-测试结果17</t>
   </si>
   <si>
-    <t>1.登录系统
-2.【测试结果】-新建，选择成果A
-3.测试结论选择不通过
-4.所有测试项勾选通过
-5.提交测试结果</t>
-  </si>
-  <si>
-    <t>1.登录系统成功
-2.进入新建界面成功，选择成果A后正常展示成果A的版本号和成果编码
-3.&lt;测试结论&gt;选择不通过成功
-4.所有测试项勾选通过成功
-5.提交报错或者提示用户测试结论与实际不符</t>
-  </si>
-  <si>
-    <t>【产品集成评测管理v1.7.1】【测试结果】【新建】-测试项全部选择通过，测试结论选择通过</t>
-  </si>
-  <si>
     <t>漏洞扫描</t>
   </si>
   <si>
     <t>新建需求-测试结果18</t>
   </si>
   <si>
-    <t>1.登录系统成功
-2.进入新建界面成功，选择成果A后正常展示成果A的版本号和成果编码
-3.&lt;测试结论&gt;选择通过成功
-4.所有测试项勾选通过成功
-5.提交测试结果成功</t>
-  </si>
-  <si>
     <t>渗透测试</t>
   </si>
   <si>
     <t>新建需求-测试结果19</t>
-  </si>
-  <si>
-    <t>【产品集成评测管理v1.7.1】【测试结果】【新建】-测试项排序验证</t>
   </si>
   <si>
     <t>软件成分分析</t>
@@ -459,28 +255,10 @@
     <t>成果A下发测试类型选择国标8项目</t>
   </si>
   <si>
-    <t>1.登录系统
-2.【测试结果】-新建，选择成果A
-3.查看测试结论位置测试项通过表展示测试项排序</t>
-  </si>
-  <si>
-    <t>1.登录系统成功
-2.进入新建界面成功，选择成果A后正常展示成果A的版本号和成果编码
-3.测试项排序为调度下发时勾选顺序</t>
-  </si>
-  <si>
-    <t>【产品集成评测管理v1.7.1】【测试结果】【新建】验证“是否包含子系统”选择"是"对输入框的显示控制</t>
-  </si>
-  <si>
     <t>代码同源分析</t>
   </si>
   <si>
     <t>新建需求-测试结果21</t>
-  </si>
-  <si>
-    <t>1.登录系统
-2.【测试结果】-新建，选择成果A
-3.&lt;是否包含子系统&gt;选择"是"</t>
   </si>
   <si>
     <t>1.登录系统成功
@@ -488,18 +266,10 @@
 3.选择"是"，显示输入框，可输入包含子系统个数</t>
   </si>
   <si>
-    <t>【产品集成评测管理v1.7.1】【测试结果】【新建】验证“是否包含子系统”选择否对输入框的显示控制</t>
-  </si>
-  <si>
     <t>知识产权检测</t>
   </si>
   <si>
     <t>新建需求-测试结果22</t>
-  </si>
-  <si>
-    <t>1.登录系统
-2.【测试结果】-新建，选择成果A
-3.&lt;是否包含子系统&gt;选择"否"</t>
   </si>
   <si>
     <t>1.登录系统成功
@@ -681,7 +451,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -1305,7 +1075,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1332,9 +1102,6 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1659,29 +1426,29 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:XEZ23"/>
-  <sheetFormatPr defaultColWidth="8.73148148148148" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.73333333333333" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="20.4537037037037" customWidth="1"/>
-    <col min="2" max="2" width="20.7314814814815" style="3" customWidth="1"/>
-    <col min="3" max="3" width="47.9537037037037" customWidth="1"/>
-    <col min="4" max="4" width="38.9722222222222" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="43.8611111111111" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="43.8611111111111" style="4" customWidth="1"/>
-    <col min="7" max="7" width="34.5555555555556" style="3" customWidth="1"/>
-    <col min="8" max="8" width="23.6481481481481" style="3" customWidth="1"/>
-    <col min="9" max="9" width="28.962962962963" style="3" customWidth="1"/>
-    <col min="10" max="10" width="31.2685185185185" style="3" customWidth="1"/>
-    <col min="11" max="11" width="23.6481481481481" style="3" customWidth="1"/>
-    <col min="12" max="12" width="15.7037037037037" customWidth="1"/>
-    <col min="13" max="13" width="15.1574074074074" customWidth="1"/>
-    <col min="14" max="14" width="36.2037037037037" customWidth="1"/>
-    <col min="15" max="15" width="17.1851851851852" customWidth="1"/>
-    <col min="16" max="16" width="12.8148148148148" customWidth="1"/>
-    <col min="17" max="16380" width="8.73148148148148" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="20.45" customWidth="1"/>
+    <col min="2" max="2" width="20.7333333333333" style="3" customWidth="1"/>
+    <col min="3" max="3" width="47.95" customWidth="1"/>
+    <col min="4" max="4" width="38.975" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="43.8583333333333" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="43.8583333333333" style="4" customWidth="1"/>
+    <col min="7" max="7" width="34.5583333333333" style="3" customWidth="1"/>
+    <col min="8" max="8" width="23.65" style="3" customWidth="1"/>
+    <col min="9" max="9" width="28.9666666666667" style="3" customWidth="1"/>
+    <col min="10" max="10" width="31.2666666666667" style="3" customWidth="1"/>
+    <col min="11" max="11" width="23.65" style="3" customWidth="1"/>
+    <col min="12" max="12" width="15.7" customWidth="1"/>
+    <col min="13" max="13" width="15.1583333333333" customWidth="1"/>
+    <col min="14" max="14" width="36.2" customWidth="1"/>
+    <col min="15" max="15" width="17.1833333333333" customWidth="1"/>
+    <col min="16" max="16" width="12.8166666666667" customWidth="1"/>
+    <col min="17" max="16380" width="8.73333333333333" hidden="1" customWidth="1"/>
     <col min="16381" max="16381" width="4.91666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="75" customHeight="1" spans="1:16380">
+    <row r="1" s="1" customFormat="1" ht="75" customHeight="1" spans="1:1024 1025:16380">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -50823,740 +50590,740 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" s="2" customFormat="1" ht="172.8" spans="2:15">
-      <c r="B2" s="7" t="s">
+    <row r="2" s="2" customFormat="1" spans="1:1024 1025:16380">
+      <c r="B2" s="7">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="F2" s="8"/>
       <c r="G2" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="I2" s="7">
+        <v>2</v>
+      </c>
+      <c r="J2" s="7">
+        <v>4</v>
+      </c>
+      <c r="K2" s="7"/>
+      <c r="N2" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="O2" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2" s="7"/>
-      <c r="N2" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="O2" s="10" t="s">
-        <v>25</v>
-      </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="187.2" spans="2:15">
-      <c r="B3" s="7" t="s">
-        <v>26</v>
+    <row r="3" s="2" customFormat="1" spans="1:1024 1025:16380">
+      <c r="B3" s="7">
+        <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="F3" s="8"/>
       <c r="G3" s="7" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>31</v>
+        <v>24</v>
+      </c>
+      <c r="I3" s="7">
+        <v>3</v>
+      </c>
+      <c r="J3" s="7">
+        <v>5</v>
       </c>
       <c r="K3" s="7"/>
-      <c r="N3" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="O3" s="10" t="s">
+      <c r="N3" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="O3" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" s="2" customFormat="1" spans="1:1024 1025:16380">
+      <c r="B4" s="7">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="4" s="2" customFormat="1" ht="187.2" spans="2:15">
-      <c r="B4" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="D4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="F4" s="8"/>
       <c r="G4" s="7" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>31</v>
+        <v>24</v>
+      </c>
+      <c r="I4" s="7">
+        <v>4</v>
+      </c>
+      <c r="J4" s="7">
+        <v>6</v>
       </c>
       <c r="K4" s="7"/>
-      <c r="N4" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="O4" s="10"/>
+      <c r="N4" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="O4" s="9"/>
     </row>
-    <row r="5" s="2" customFormat="1" ht="330" customHeight="1" spans="2:15">
-      <c r="B5" s="7" t="s">
-        <v>36</v>
+    <row r="5" s="2" customFormat="1" ht="330" customHeight="1" spans="1:1024 1025:16380">
+      <c r="B5" s="7">
+        <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="F5" s="8"/>
       <c r="G5" s="7" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>41</v>
+        <v>29</v>
+      </c>
+      <c r="I5" s="7">
+        <v>5</v>
+      </c>
+      <c r="J5" s="7">
+        <v>7</v>
       </c>
       <c r="K5" s="7"/>
-      <c r="N5" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="O5" s="10"/>
+      <c r="N5" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="O5" s="9"/>
     </row>
-    <row r="6" s="2" customFormat="1" ht="330" customHeight="1" spans="2:15">
-      <c r="B6" s="7" t="s">
-        <v>42</v>
+    <row r="6" s="2" customFormat="1" ht="330" customHeight="1" spans="1:1024 1025:16380">
+      <c r="B6" s="7">
+        <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="7" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>41</v>
+        <v>29</v>
+      </c>
+      <c r="I6" s="7">
+        <v>6</v>
+      </c>
+      <c r="J6" s="7">
+        <v>8</v>
       </c>
       <c r="K6" s="7"/>
-      <c r="N6" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="O6" s="10"/>
+      <c r="N6" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="O6" s="9"/>
     </row>
-    <row r="7" s="2" customFormat="1" ht="409" customHeight="1" spans="2:15">
-      <c r="B7" s="7" t="s">
-        <v>45</v>
+    <row r="7" s="2" customFormat="1" ht="409" customHeight="1" spans="1:1024 1025:16380">
+      <c r="B7" s="7">
+        <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="7" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>49</v>
+        <v>29</v>
+      </c>
+      <c r="I7" s="7">
+        <v>7</v>
+      </c>
+      <c r="J7" s="7">
+        <v>9</v>
       </c>
       <c r="K7" s="7"/>
-      <c r="N7" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="O7" s="10" t="s">
-        <v>25</v>
+      <c r="N7" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="O7" s="9" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" ht="409" customHeight="1" spans="2:15">
-      <c r="B8" s="7" t="s">
-        <v>50</v>
+    <row r="8" s="2" customFormat="1" ht="409" customHeight="1" spans="1:1024 1025:16380">
+      <c r="B8" s="7">
+        <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="F8" s="8"/>
       <c r="G8" s="7" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>55</v>
+        <v>36</v>
+      </c>
+      <c r="I8" s="7">
+        <v>8</v>
+      </c>
+      <c r="J8" s="7">
+        <v>10</v>
       </c>
       <c r="K8" s="7"/>
-      <c r="N8" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="O8" s="10" t="s">
-        <v>25</v>
+      <c r="N8" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="O8" s="9" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" ht="409" customHeight="1" spans="2:15">
-      <c r="B9" s="7" t="s">
-        <v>56</v>
+    <row r="9" s="2" customFormat="1" ht="409" customHeight="1" spans="1:1024 1025:16380">
+      <c r="B9" s="7">
+        <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="F9" s="8"/>
       <c r="G9" s="7" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>61</v>
+        <v>39</v>
+      </c>
+      <c r="I9" s="7">
+        <v>9</v>
+      </c>
+      <c r="J9" s="7">
+        <v>11</v>
       </c>
       <c r="K9" s="7"/>
-      <c r="N9" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="O9" s="10" t="s">
-        <v>25</v>
+      <c r="N9" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="O9" s="9" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" ht="409" customHeight="1" spans="2:15">
-      <c r="B10" s="7" t="s">
-        <v>62</v>
+    <row r="10" s="2" customFormat="1" ht="409" customHeight="1" spans="1:1024 1025:16380">
+      <c r="B10" s="7">
+        <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="D10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="F10" s="8"/>
       <c r="G10" s="7" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>67</v>
+        <v>42</v>
+      </c>
+      <c r="I10" s="7">
+        <v>10</v>
+      </c>
+      <c r="J10" s="7">
+        <v>12</v>
       </c>
       <c r="K10" s="7"/>
-      <c r="N10" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="O10" s="10" t="s">
-        <v>25</v>
+      <c r="N10" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="O10" s="9" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="11" s="2" customFormat="1" ht="409" customHeight="1" spans="2:15">
-      <c r="B11" s="7" t="s">
-        <v>68</v>
+    <row r="11" s="2" customFormat="1" ht="409" customHeight="1" spans="1:1024 1025:16380">
+      <c r="B11" s="7">
+        <v>10</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="D11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="F11" s="8"/>
       <c r="G11" s="7" t="s">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>71</v>
+        <v>42</v>
+      </c>
+      <c r="I11" s="7">
+        <v>11</v>
+      </c>
+      <c r="J11" s="7">
+        <v>13</v>
       </c>
       <c r="K11" s="7"/>
-      <c r="N11" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="O11" s="10" t="s">
-        <v>25</v>
+      <c r="N11" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="O11" s="9" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="12" s="2" customFormat="1" ht="409" customHeight="1" spans="2:15">
-      <c r="B12" s="7" t="s">
-        <v>72</v>
+    <row r="12" s="2" customFormat="1" ht="409" customHeight="1" spans="1:1024 1025:16380">
+      <c r="B12" s="7">
+        <v>11</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="D12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="F12" s="8"/>
       <c r="G12" s="7" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>76</v>
+        <v>47</v>
+      </c>
+      <c r="I12" s="7">
+        <v>12</v>
+      </c>
+      <c r="J12" s="7">
+        <v>14</v>
       </c>
       <c r="K12" s="7"/>
-      <c r="N12" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="O12" s="10" t="s">
-        <v>25</v>
+      <c r="N12" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="O12" s="9" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="13" s="2" customFormat="1" ht="409" customHeight="1" spans="2:15">
-      <c r="B13" s="9" t="s">
-        <v>77</v>
+    <row r="13" s="2" customFormat="1" ht="409" customHeight="1" spans="1:1024 1025:16380">
+      <c r="B13" s="7">
+        <v>12</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="F13" s="8"/>
       <c r="G13" s="7" t="s">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>81</v>
+        <v>50</v>
+      </c>
+      <c r="I13" s="7">
+        <v>13</v>
+      </c>
+      <c r="J13" s="7">
+        <v>15</v>
       </c>
       <c r="K13" s="7"/>
-      <c r="N13" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="O13" s="10" t="s">
-        <v>25</v>
+      <c r="N13" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="O13" s="9" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="14" s="2" customFormat="1" ht="409" customHeight="1" spans="2:15">
-      <c r="B14" s="9" t="s">
-        <v>77</v>
+    <row r="14" s="2" customFormat="1" ht="409" customHeight="1" spans="1:1024 1025:16380">
+      <c r="B14" s="7">
+        <v>13</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="D14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="F14" s="8"/>
       <c r="G14" s="7" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>81</v>
+        <v>50</v>
+      </c>
+      <c r="I14" s="7">
+        <v>14</v>
+      </c>
+      <c r="J14" s="7">
+        <v>16</v>
       </c>
       <c r="K14" s="7"/>
-      <c r="N14" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="O14" s="10" t="s">
-        <v>25</v>
+      <c r="N14" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="O14" s="9" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="15" s="2" customFormat="1" ht="409" customHeight="1" spans="2:15">
-      <c r="B15" s="9" t="s">
-        <v>84</v>
+    <row r="15" s="2" customFormat="1" ht="409" customHeight="1" spans="1:1024 1025:16380">
+      <c r="B15" s="7">
+        <v>14</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>85</v>
+        <v>53</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="F15" s="8"/>
       <c r="G15" s="7" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="H15" s="7"/>
-      <c r="I15" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>87</v>
+      <c r="I15" s="7">
+        <v>15</v>
+      </c>
+      <c r="J15" s="7">
+        <v>17</v>
       </c>
       <c r="K15" s="7"/>
-      <c r="N15" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="O15" s="10" t="s">
-        <v>25</v>
+      <c r="N15" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="O15" s="9" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="16" s="2" customFormat="1" ht="409" customHeight="1" spans="2:15">
-      <c r="B16" s="9" t="s">
-        <v>88</v>
+    <row r="16" s="2" customFormat="1" ht="409" customHeight="1" spans="1:1024 1025:16380">
+      <c r="B16" s="7">
+        <v>15</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>89</v>
+        <v>55</v>
       </c>
       <c r="D16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="F16" s="8"/>
       <c r="G16" s="7" t="s">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="J16" s="7" t="s">
-        <v>93</v>
+        <v>57</v>
+      </c>
+      <c r="I16" s="7">
+        <v>16</v>
+      </c>
+      <c r="J16" s="7">
+        <v>18</v>
       </c>
       <c r="K16" s="7"/>
-      <c r="N16" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="O16" s="10" t="s">
-        <v>25</v>
+      <c r="N16" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="O16" s="9" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" ht="409" customHeight="1" spans="2:15">
-      <c r="B17" s="9" t="s">
-        <v>94</v>
+      <c r="B17" s="7">
+        <v>16</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>95</v>
+        <v>58</v>
       </c>
       <c r="D17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="F17" s="8"/>
       <c r="G17" s="7" t="s">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="J17" s="7" t="s">
-        <v>98</v>
+        <v>57</v>
+      </c>
+      <c r="I17" s="7">
+        <v>17</v>
+      </c>
+      <c r="J17" s="7">
+        <v>19</v>
       </c>
       <c r="K17" s="7"/>
-      <c r="N17" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="O17" s="10" t="s">
-        <v>25</v>
+      <c r="N17" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="O17" s="9" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" ht="409" customHeight="1" spans="2:15">
-      <c r="B18" s="9" t="s">
-        <v>99</v>
+      <c r="B18" s="7">
+        <v>17</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="F18" s="8"/>
       <c r="G18" s="7" t="s">
-        <v>101</v>
+        <v>61</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="I18" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="J18" s="7" t="s">
-        <v>103</v>
+        <v>57</v>
+      </c>
+      <c r="I18" s="7">
+        <v>18</v>
+      </c>
+      <c r="J18" s="7">
+        <v>20</v>
       </c>
       <c r="K18" s="7"/>
-      <c r="N18" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="O18" s="10" t="s">
-        <v>25</v>
+      <c r="N18" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="O18" s="9" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" ht="409" customHeight="1" spans="2:15">
-      <c r="B19" s="9" t="s">
-        <v>104</v>
+      <c r="B19" s="7">
+        <v>18</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>105</v>
+        <v>62</v>
       </c>
       <c r="D19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="F19" s="8"/>
       <c r="G19" s="7" t="s">
-        <v>106</v>
+        <v>63</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>107</v>
+        <v>57</v>
+      </c>
+      <c r="I19" s="7">
+        <v>19</v>
+      </c>
+      <c r="J19" s="7">
+        <v>21</v>
       </c>
       <c r="K19" s="7"/>
-      <c r="N19" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="O19" s="10" t="s">
-        <v>25</v>
+      <c r="N19" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="O19" s="9" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" ht="409" customHeight="1" spans="2:15">
-      <c r="B20" s="9" t="s">
-        <v>104</v>
+      <c r="B20" s="7">
+        <v>19</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>108</v>
+        <v>64</v>
       </c>
       <c r="D20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="F20" s="8"/>
       <c r="G20" s="7" t="s">
-        <v>109</v>
+        <v>65</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="J20" s="7" t="s">
-        <v>107</v>
+        <v>57</v>
+      </c>
+      <c r="I20" s="7">
+        <v>20</v>
+      </c>
+      <c r="J20" s="7">
+        <v>22</v>
       </c>
       <c r="K20" s="7"/>
-      <c r="N20" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="O20" s="10" t="s">
-        <v>25</v>
+      <c r="N20" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="O20" s="9" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" ht="409" customHeight="1" spans="2:15">
-      <c r="B21" s="9" t="s">
-        <v>110</v>
+      <c r="B21" s="7">
+        <v>20</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>111</v>
+        <v>66</v>
       </c>
       <c r="D21" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="F21" s="8"/>
       <c r="G21" s="7" t="s">
-        <v>112</v>
+        <v>67</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="J21" s="7" t="s">
-        <v>115</v>
+        <v>68</v>
+      </c>
+      <c r="I21" s="7">
+        <v>21</v>
+      </c>
+      <c r="J21" s="7">
+        <v>23</v>
       </c>
       <c r="K21" s="7"/>
-      <c r="N21" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="O21" s="10" t="s">
-        <v>25</v>
+      <c r="N21" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="O21" s="9" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" ht="409" customHeight="1" spans="2:15">
-      <c r="B22" s="9" t="s">
-        <v>116</v>
+      <c r="B22" s="7">
+        <v>21</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>117</v>
+        <v>69</v>
       </c>
       <c r="D22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="F22" s="8"/>
       <c r="G22" s="7" t="s">
-        <v>118</v>
+        <v>70</v>
       </c>
       <c r="H22" s="7"/>
-      <c r="I22" s="7" t="s">
-        <v>119</v>
+      <c r="I22" s="7">
+        <v>22</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>120</v>
+        <v>71</v>
       </c>
       <c r="K22" s="7"/>
-      <c r="N22" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="O22" s="10" t="s">
-        <v>25</v>
+      <c r="N22" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="O22" s="9" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" ht="409" customHeight="1" spans="2:15">
-      <c r="B23" s="9" t="s">
-        <v>121</v>
+      <c r="B23" s="7">
+        <v>22</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>122</v>
+        <v>72</v>
       </c>
       <c r="D23" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="F23" s="8"/>
       <c r="G23" s="7" t="s">
-        <v>123</v>
+        <v>73</v>
       </c>
       <c r="H23" s="7"/>
-      <c r="I23" s="7" t="s">
-        <v>124</v>
+      <c r="I23" s="7">
+        <v>23</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>125</v>
+        <v>74</v>
       </c>
       <c r="K23" s="7"/>
-      <c r="N23" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="O23" s="10" t="s">
-        <v>25</v>
+      <c r="N23" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="O23" s="9" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -51565,12 +51332,12 @@
       <formula1>1</formula1>
       <formula2>100</formula2>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1 C2 C3:C1048576">
+      <formula1>"功能性,性能效率,兼容性,易用性,信息安全性,维护性,可移植性,业务场景,接口(OpenAPI),二开能力,研发全流程上云,研发云CI/CD,底座集成能力,组件适配能力,用户文档集,病毒扫描,漏洞扫描,渗透测试,软件成分分析,代码同源分析,知识产权检测"</formula1>
+    </dataValidation>
     <dataValidation type="textLength" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="关联需求" error="关联需求不超过40字符" sqref="D1">
       <formula1>0</formula1>
       <formula2>40</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1 G2:G4 G5:G23 G24:G1048576">
-      <formula1>"新建需求-测试结果1,新建需求-测试结果2,新建需求-测试结果3,新建需求-测试结果4,新建需求-测试结果5,新建需求-测试结果6,新建需求-测试结果7,新建需求-测试结果8,新建需求-测试结果9,新建需求-测试结果10,新建需求-测试结果11,新建需求-测试结果12,新建需求-测试结果13,新建需求-测试结果14,新建需求-测试结果15,新建需求-测试结果16,新建需求-测试结果17,新建需求-测试结果18,新建需求-测试结果19,新建需求-测试结果20,新建需求-测试结果21,新建需求-测试结果22"</formula1>
     </dataValidation>
     <dataValidation type="textLength" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="说明" error="说明不超过300字符" sqref="H1">
       <formula1>0</formula1>
@@ -51588,35 +51355,35 @@
       <formula1>0</formula1>
       <formula2>1000</formula2>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N1 N2 N3 N4 N5 N6 N7 N8 N9 N10 N11 N12 N13 N14 N15 N16 N17 N18 N19 N20 N21 N22 N23 N24:N1048576"/>
-    <dataValidation type="textLength" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="用例ID" error="用例ID不超过30字符" sqref="A2 A3 A4 A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18 A19 A20 A21 A22 A23 A24:A1048576">
+    <dataValidation type="textLength" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="用例ID" error="用例ID不超过30字符" sqref="A2:A1048576">
       <formula1>0</formula1>
       <formula2>30</formula2>
     </dataValidation>
-    <dataValidation type="textLength" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="用例名称" error="用例名称不超过100字符" sqref="B2 B3 B4 B5 B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B17 B18 B19 B20 B21 B22 B23 B24:B1048576">
+    <dataValidation type="textLength" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="用例名称" error="用例名称不超过100字符" sqref="B2:B23 B24:B1048576">
       <formula1>1</formula1>
       <formula2>100</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="级别" error="级别只能选择P1、P2、P3、P4" sqref="D2 D3 D4 D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24:D1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="级别" error="级别只能选择P1、P2、P3、P4" sqref="D2:D1048576">
       <formula1>"P1,P2,P3,P4"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="评审状态" error="评审状态只能选择草稿、待评审、通过、不通过" sqref="E2 E3 E4 E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24:E1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="评审状态" error="评审状态只能选择草稿、待评审、通过、不通过" sqref="E2:E1048576">
       <formula1>"草稿,待评审,通过,不通过"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" errorTitle="关联需求" error="关联需求不超过100字符" sqref="F2 F3 F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24:F1048576"/>
-    <dataValidation type="textLength" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="前置条件" error="前置条件不超过3000字符" sqref="H2 H3 H4 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24:H1048576">
+    <dataValidation allowBlank="1" showInputMessage="1" errorTitle="关联需求" error="关联需求不超过100字符" sqref="F2:F1048576"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G$1:G$1048576">
+      <formula1>"新建需求-测试结果1,新建需求-测试结果2,新建需求-测试结果3,新建需求-测试结果4,新建需求-测试结果5,新建需求-测试结果6,新建需求-测试结果7,新建需求-测试结果8,新建需求-测试结果9,新建需求-测试结果10,新建需求-测试结果11,新建需求-测试结果12,新建需求-测试结果13,新建需求-测试结果14,新建需求-测试结果15,新建需求-测试结果16,新建需求-测试结果17,新建需求-测试结果18,新建需求-测试结果19,新建需求-测试结果20,新建需求-测试结果21,新建需求-测试结果22"</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="前置条件" error="前置条件不超过3000字符" sqref="H2:H1048576">
       <formula1>0</formula1>
       <formula2>3000</formula2>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" errorTitle="步骤描述" error="步骤描述不超过1000字符" sqref="I2 I3 I4 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24:I1048576"/>
-    <dataValidation allowBlank="1" showInputMessage="1" errorTitle="预期结果" error="预期结果不超过1000字符" sqref="J2 J3 J4 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24:J1048576"/>
-    <dataValidation type="textLength" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="说明" error="说明不超过3000字符" sqref="K2 K3 K4 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K24:K1048576">
+    <dataValidation allowBlank="1" showInputMessage="1" errorTitle="步骤描述" error="步骤描述不超过1000字符" sqref="I2:I23 I24:I1048576"/>
+    <dataValidation allowBlank="1" showInputMessage="1" errorTitle="预期结果" error="预期结果不超过1000字符" sqref="J2:J21 J22:J1048576"/>
+    <dataValidation type="textLength" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="说明" error="说明不超过3000字符" sqref="K2:K1048576">
       <formula1>0</formula1>
       <formula2>3000</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C$1:C$1048576">
-      <formula1>"功能性,性能效率,兼容性,易用性,信息安全性,维护性,可移植性,业务场景,接口(OpenAPI),二开能力,研发全流程上云,研发云CI/CD,底座集成能力,组件适配能力,用户文档集,病毒扫描,漏洞扫描,渗透测试,软件成分分析,代码同源分析,知识产权检测"</formula1>
-    </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N$1:N$1048576"/>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -51627,38 +51394,38 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultColWidth="8.62037037037037" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="8.61666666666667" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="2" max="2" width="20.7685185185185" customWidth="1"/>
-    <col min="3" max="3" width="21.7777777777778" customWidth="1"/>
+    <col min="2" max="2" width="20.7666666666667" customWidth="1"/>
+    <col min="3" max="3" width="21.775" customWidth="1"/>
     <col min="4" max="4" width="16.75" customWidth="1"/>
-    <col min="5" max="5" width="16.8240740740741" customWidth="1"/>
-    <col min="6" max="6" width="16.212962962963" customWidth="1"/>
-    <col min="7" max="7" width="24.0925925925926" customWidth="1"/>
-    <col min="8" max="8" width="19.0648148148148" customWidth="1"/>
+    <col min="5" max="5" width="16.825" customWidth="1"/>
+    <col min="6" max="6" width="16.2166666666667" customWidth="1"/>
+    <col min="7" max="7" width="24.0916666666667" customWidth="1"/>
+    <col min="8" max="8" width="19.0666666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>126</v>
+        <v>75</v>
       </c>
       <c r="B1" t="s">
-        <v>127</v>
+        <v>76</v>
       </c>
       <c r="C1" t="s">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="D1" t="s">
-        <v>129</v>
+        <v>78</v>
       </c>
       <c r="E1" t="s">
-        <v>130</v>
+        <v>79</v>
       </c>
       <c r="F1" t="s">
-        <v>131</v>
+        <v>80</v>
       </c>
       <c r="G1" t="s">
-        <v>132</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -51666,22 +51433,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>133</v>
+        <v>82</v>
       </c>
       <c r="C2" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>135</v>
+        <v>84</v>
       </c>
       <c r="E2" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="F2" t="s">
-        <v>137</v>
+        <v>86</v>
       </c>
       <c r="G2" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -51689,22 +51456,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>138</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s">
-        <v>135</v>
+        <v>84</v>
       </c>
       <c r="E3" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="F3" t="s">
-        <v>137</v>
+        <v>86</v>
       </c>
       <c r="G3" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -51712,22 +51479,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>139</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>135</v>
+        <v>84</v>
       </c>
       <c r="E4" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="F4" t="s">
-        <v>137</v>
+        <v>86</v>
       </c>
       <c r="G4" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -51735,22 +51502,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>140</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>135</v>
+        <v>84</v>
       </c>
       <c r="E5" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="F5" t="s">
-        <v>137</v>
+        <v>86</v>
       </c>
       <c r="G5" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -51758,22 +51525,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>141</v>
+        <v>90</v>
       </c>
       <c r="C6" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>135</v>
+        <v>84</v>
       </c>
       <c r="E6" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="F6" t="s">
-        <v>137</v>
+        <v>86</v>
       </c>
       <c r="G6" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -51781,22 +51548,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>142</v>
+        <v>91</v>
       </c>
       <c r="C7" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>135</v>
+        <v>84</v>
       </c>
       <c r="E7" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="F7" t="s">
-        <v>137</v>
+        <v>86</v>
       </c>
       <c r="G7" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -51804,22 +51571,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>143</v>
+        <v>92</v>
       </c>
       <c r="C8" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
-        <v>135</v>
+        <v>84</v>
       </c>
       <c r="E8" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="F8" t="s">
-        <v>137</v>
+        <v>86</v>
       </c>
       <c r="G8" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -51827,22 +51594,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>144</v>
+        <v>93</v>
       </c>
       <c r="C9" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="D9" t="s">
-        <v>135</v>
+        <v>84</v>
       </c>
       <c r="E9" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="F9" t="s">
-        <v>137</v>
+        <v>86</v>
       </c>
       <c r="G9" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -51850,22 +51617,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>145</v>
+        <v>94</v>
       </c>
       <c r="C10" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="D10" t="s">
-        <v>135</v>
+        <v>84</v>
       </c>
       <c r="E10" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="F10" t="s">
-        <v>137</v>
+        <v>86</v>
       </c>
       <c r="G10" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -51873,22 +51640,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>146</v>
+        <v>95</v>
       </c>
       <c r="C11" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>135</v>
+        <v>84</v>
       </c>
       <c r="E11" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="F11" t="s">
-        <v>137</v>
+        <v>86</v>
       </c>
       <c r="G11" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -51896,97 +51663,97 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>147</v>
+        <v>96</v>
       </c>
       <c r="C12" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="D12" t="s">
-        <v>135</v>
+        <v>84</v>
       </c>
       <c r="E12" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="F12" t="s">
-        <v>137</v>
+        <v>86</v>
       </c>
       <c r="G12" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
     </row>
-    <row r="13" spans="7:7">
+    <row r="13" spans="1:7">
       <c r="G13" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
     </row>
-    <row r="14" spans="7:7">
+    <row r="14" spans="1:7">
       <c r="G14" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
     </row>
-    <row r="15" spans="7:7">
+    <row r="15" spans="1:7">
       <c r="G15" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
     </row>
-    <row r="16" spans="7:7">
+    <row r="16" spans="1:7">
       <c r="G16" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="7:7">
       <c r="G17" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="7:7">
       <c r="G18" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" spans="7:7">
       <c r="G19" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" spans="7:7">
       <c r="G20" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21" spans="7:7">
       <c r="G21" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" spans="7:7">
       <c r="G22" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" spans="7:7">
       <c r="G23" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24" spans="7:7">
       <c r="G24" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
     </row>
     <row r="25" spans="7:7">
       <c r="G25" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26" spans="7:7">
       <c r="G26" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" spans="7:7">
       <c r="G27" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -51999,17 +51766,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B35"/>
-  <sheetFormatPr defaultColWidth="8.62037037037037" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="8.61666666666667" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <cols>
-    <col min="2" max="2" width="26.9537037037037" customWidth="1"/>
+    <col min="2" max="2" width="26.95" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>126</v>
+        <v>75</v>
       </c>
       <c r="B1" t="s">
-        <v>148</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -52017,7 +51784,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>149</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -52025,7 +51792,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>150</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -52033,7 +51800,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>151</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -52041,7 +51808,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>152</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -52049,7 +51816,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>153</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -52057,7 +51824,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>154</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -52065,7 +51832,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>155</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -52073,7 +51840,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>156</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -52081,7 +51848,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>157</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -52089,7 +51856,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>158</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -52097,7 +51864,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>159</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -52105,7 +51872,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>160</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -52113,7 +51880,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -52121,7 +51888,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -52129,7 +51896,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>163</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -52137,7 +51904,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>164</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -52145,7 +51912,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>165</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -52153,7 +51920,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>166</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -52161,7 +51928,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>167</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -52169,7 +51936,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>168</v>
+        <v>117</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -52177,7 +51944,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -52185,7 +51952,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -52193,7 +51960,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>171</v>
+        <v>120</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -52201,7 +51968,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>172</v>
+        <v>121</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -52209,7 +51976,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>173</v>
+        <v>122</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -52217,7 +51984,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>174</v>
+        <v>123</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -52225,7 +51992,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>175</v>
+        <v>124</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -52233,7 +52000,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>176</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -52241,7 +52008,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>177</v>
+        <v>126</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -52249,7 +52016,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>178</v>
+        <v>127</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -52257,7 +52024,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>179</v>
+        <v>128</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -52265,7 +52032,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>180</v>
+        <v>129</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -52273,7 +52040,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>181</v>
+        <v>130</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -52281,7 +52048,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>182</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
